--- a/Data/EXCEL/Transfer/salemon/202206/6696-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6696-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EABBF5A-B643-43F5-BE49-0F1C4178D414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D50B0FA1-917B-480F-8383-1EC3E89005D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6696-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -1218,14 +1218,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.25" customWidth="1"/>
-    <col min="2" max="6" width="11.125" customWidth="1"/>
-    <col min="7" max="7" width="12.125" customWidth="1"/>
-    <col min="8" max="16" width="10.5" customWidth="1"/>
-    <col min="17" max="17" width="11.75" customWidth="1"/>
+    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="2" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="13.875" customWidth="1"/>
+    <col min="8" max="16" width="12.125" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1378,25 +1378,25 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="C5" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D5" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E5" s="7">
-        <v>162.5</v>
+        <v>191.5</v>
       </c>
       <c r="F5" s="8">
-        <v>-25</v>
+        <v>-1</v>
       </c>
       <c r="G5" s="8">
-        <v>-11.06</v>
+        <v>-0.5</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -1431,25 +1431,25 @@
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="C6" s="7">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="D6" s="7">
-        <v>266</v>
+        <v>232</v>
       </c>
       <c r="E6" s="7">
-        <v>190</v>
+        <v>162.5</v>
       </c>
       <c r="F6" s="8">
-        <v>-30</v>
+        <v>-25</v>
       </c>
       <c r="G6" s="8">
-        <v>-11.72</v>
+        <v>-11.06</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -1484,25 +1484,25 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C7" s="7">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="D7" s="7">
-        <v>271.5</v>
+        <v>266</v>
       </c>
       <c r="E7" s="7">
-        <v>214.5</v>
-      </c>
-      <c r="F7" s="10">
-        <v>8</v>
-      </c>
-      <c r="G7" s="10">
-        <v>3.23</v>
+        <v>190</v>
+      </c>
+      <c r="F7" s="8">
+        <v>-30</v>
+      </c>
+      <c r="G7" s="8">
+        <v>-11.72</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -1537,25 +1537,25 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="C8" s="7">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="D8" s="7">
-        <v>253</v>
+        <v>271.5</v>
       </c>
       <c r="E8" s="7">
-        <v>205</v>
+        <v>214.5</v>
       </c>
       <c r="F8" s="10">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="G8" s="10">
-        <v>16.98</v>
+        <v>3.23</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -1590,25 +1590,25 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="C9" s="7">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="D9" s="7">
-        <v>222.5</v>
+        <v>253</v>
       </c>
       <c r="E9" s="7">
-        <v>184.5</v>
+        <v>205</v>
       </c>
       <c r="F9" s="10">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G9" s="10">
-        <v>13.98</v>
+        <v>16.98</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -1643,25 +1643,25 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C10" s="7">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="D10" s="7">
-        <v>232</v>
+        <v>222.5</v>
       </c>
       <c r="E10" s="7">
-        <v>184</v>
-      </c>
-      <c r="F10" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G10" s="8">
-        <v>-1.06</v>
+        <v>184.5</v>
+      </c>
+      <c r="F10" s="10">
+        <v>26</v>
+      </c>
+      <c r="G10" s="10">
+        <v>13.98</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -1696,25 +1696,25 @@
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="C11" s="7">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D11" s="7">
-        <v>189.5</v>
+        <v>232</v>
       </c>
       <c r="E11" s="7">
-        <v>123.5</v>
-      </c>
-      <c r="F11" s="10">
-        <v>61</v>
-      </c>
-      <c r="G11" s="10">
-        <v>48.03</v>
+        <v>184</v>
+      </c>
+      <c r="F11" s="8">
+        <v>-2</v>
+      </c>
+      <c r="G11" s="8">
+        <v>-1.06</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -1749,25 +1749,25 @@
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C12" s="7">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="D12" s="7">
-        <v>146</v>
+        <v>189.5</v>
       </c>
       <c r="E12" s="7">
-        <v>124.5</v>
-      </c>
-      <c r="F12" s="8">
-        <v>-10</v>
-      </c>
-      <c r="G12" s="8">
-        <v>-7.3</v>
+        <v>123.5</v>
+      </c>
+      <c r="F12" s="10">
+        <v>61</v>
+      </c>
+      <c r="G12" s="10">
+        <v>48.03</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
@@ -1802,25 +1802,25 @@
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="C13" s="7">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D13" s="7">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="E13" s="7">
-        <v>135.5</v>
+        <v>124.5</v>
       </c>
       <c r="F13" s="8">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="G13" s="8">
-        <v>-15.43</v>
+        <v>-7.3</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
@@ -1855,25 +1855,25 @@
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="C14" s="7">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="D14" s="7">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E14" s="7">
-        <v>132</v>
-      </c>
-      <c r="F14" s="10">
-        <v>17</v>
-      </c>
-      <c r="G14" s="10">
-        <v>11.72</v>
+        <v>135.5</v>
+      </c>
+      <c r="F14" s="8">
+        <v>-25</v>
+      </c>
+      <c r="G14" s="8">
+        <v>-15.43</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -1908,25 +1908,25 @@
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>229.5</v>
+        <v>145</v>
       </c>
       <c r="C15" s="7">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="D15" s="7">
-        <v>233</v>
+        <v>171</v>
       </c>
       <c r="E15" s="7">
-        <v>133</v>
-      </c>
-      <c r="F15" s="8">
-        <v>-84.5</v>
-      </c>
-      <c r="G15" s="8">
-        <v>-36.82</v>
+        <v>132</v>
+      </c>
+      <c r="F15" s="10">
+        <v>17</v>
+      </c>
+      <c r="G15" s="10">
+        <v>11.72</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -1961,25 +1961,25 @@
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>238</v>
+        <v>229.5</v>
       </c>
       <c r="C16" s="7">
-        <v>229.5</v>
+        <v>145</v>
       </c>
       <c r="D16" s="7">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E16" s="7">
-        <v>207</v>
+        <v>133</v>
       </c>
       <c r="F16" s="8">
-        <v>-8.5</v>
+        <v>-84.5</v>
       </c>
       <c r="G16" s="8">
-        <v>-3.57</v>
+        <v>-36.82</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
@@ -2014,25 +2014,25 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>262.5</v>
+        <v>238</v>
       </c>
       <c r="C17" s="7">
-        <v>238</v>
+        <v>229.5</v>
       </c>
       <c r="D17" s="7">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="E17" s="7">
-        <v>187.5</v>
+        <v>207</v>
       </c>
       <c r="F17" s="8">
-        <v>-24.5</v>
+        <v>-8.5</v>
       </c>
       <c r="G17" s="8">
-        <v>-9.33</v>
+        <v>-3.57</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -2067,25 +2067,25 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>195.5</v>
+        <v>262.5</v>
       </c>
       <c r="C18" s="7">
-        <v>262.5</v>
+        <v>238</v>
       </c>
       <c r="D18" s="7">
-        <v>301</v>
+        <v>265</v>
       </c>
       <c r="E18" s="7">
-        <v>181</v>
-      </c>
-      <c r="F18" s="10">
-        <v>67</v>
-      </c>
-      <c r="G18" s="10">
-        <v>34.270000000000003</v>
+        <v>187.5</v>
+      </c>
+      <c r="F18" s="8">
+        <v>-24.5</v>
+      </c>
+      <c r="G18" s="8">
+        <v>-9.33</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
@@ -2120,25 +2120,25 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>129</v>
+        <v>195.5</v>
       </c>
       <c r="C19" s="7">
-        <v>195.5</v>
+        <v>262.5</v>
       </c>
       <c r="D19" s="7">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="E19" s="7">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="F19" s="10">
-        <v>66.5</v>
+        <v>67</v>
       </c>
       <c r="G19" s="10">
-        <v>51.55</v>
+        <v>34.270000000000003</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
@@ -2173,25 +2173,25 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>106.5</v>
+        <v>129</v>
       </c>
       <c r="C20" s="7">
+        <v>195.5</v>
+      </c>
+      <c r="D20" s="7">
+        <v>197</v>
+      </c>
+      <c r="E20" s="7">
         <v>129</v>
       </c>
-      <c r="D20" s="7">
-        <v>150</v>
-      </c>
-      <c r="E20" s="7">
-        <v>107</v>
-      </c>
       <c r="F20" s="10">
-        <v>22.5</v>
+        <v>66.5</v>
       </c>
       <c r="G20" s="10">
-        <v>21.13</v>
+        <v>51.55</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -2226,25 +2226,25 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>102</v>
+        <v>106.5</v>
       </c>
       <c r="C21" s="7">
-        <v>106.5</v>
+        <v>129</v>
       </c>
       <c r="D21" s="7">
-        <v>122.5</v>
+        <v>150</v>
       </c>
       <c r="E21" s="7">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F21" s="10">
-        <v>4.5</v>
+        <v>22.5</v>
       </c>
       <c r="G21" s="10">
-        <v>4.41</v>
+        <v>21.13</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
@@ -2279,25 +2279,25 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C22" s="7">
-        <v>102</v>
+        <v>106.5</v>
       </c>
       <c r="D22" s="7">
-        <v>106</v>
+        <v>122.5</v>
       </c>
       <c r="E22" s="7">
-        <v>99</v>
-      </c>
-      <c r="F22" s="8">
-        <v>-4</v>
-      </c>
-      <c r="G22" s="8">
-        <v>-3.77</v>
+        <v>103</v>
+      </c>
+      <c r="F22" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="G22" s="10">
+        <v>4.41</v>
       </c>
       <c r="H22" s="9">
         <v>0</v>
@@ -2332,25 +2332,25 @@
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>100.5</v>
+        <v>106</v>
       </c>
       <c r="C23" s="7">
+        <v>102</v>
+      </c>
+      <c r="D23" s="7">
         <v>106</v>
       </c>
-      <c r="D23" s="7">
-        <v>115.5</v>
-      </c>
       <c r="E23" s="7">
-        <v>96.7</v>
-      </c>
-      <c r="F23" s="10">
-        <v>5.5</v>
-      </c>
-      <c r="G23" s="10">
-        <v>5.47</v>
+        <v>99</v>
+      </c>
+      <c r="F23" s="8">
+        <v>-4</v>
+      </c>
+      <c r="G23" s="8">
+        <v>-3.77</v>
       </c>
       <c r="H23" s="9">
         <v>0</v>
@@ -2385,25 +2385,25 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
-        <v>105</v>
+        <v>100.5</v>
       </c>
       <c r="C24" s="7">
-        <v>100.5</v>
+        <v>106</v>
       </c>
       <c r="D24" s="7">
-        <v>106.5</v>
+        <v>115.5</v>
       </c>
       <c r="E24" s="7">
-        <v>99.7</v>
-      </c>
-      <c r="F24" s="8">
-        <v>-4.5</v>
-      </c>
-      <c r="G24" s="8">
-        <v>-4.29</v>
+        <v>96.7</v>
+      </c>
+      <c r="F24" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="G24" s="10">
+        <v>5.47</v>
       </c>
       <c r="H24" s="9">
         <v>0</v>
@@ -2438,25 +2438,25 @@
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7">
-        <v>113.5</v>
+        <v>105</v>
       </c>
       <c r="C25" s="7">
-        <v>105</v>
+        <v>100.5</v>
       </c>
       <c r="D25" s="7">
-        <v>127</v>
+        <v>106.5</v>
       </c>
       <c r="E25" s="7">
-        <v>103.5</v>
+        <v>99.7</v>
       </c>
       <c r="F25" s="8">
-        <v>-8.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G25" s="8">
-        <v>-7.49</v>
+        <v>-4.29</v>
       </c>
       <c r="H25" s="9">
         <v>0</v>
@@ -2491,25 +2491,25 @@
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7">
-        <v>116</v>
+        <v>113.5</v>
       </c>
       <c r="C26" s="7">
-        <v>113.5</v>
+        <v>105</v>
       </c>
       <c r="D26" s="7">
-        <v>117.5</v>
+        <v>127</v>
       </c>
       <c r="E26" s="7">
-        <v>99.5</v>
+        <v>103.5</v>
       </c>
       <c r="F26" s="8">
-        <v>-2.5</v>
+        <v>-8.5</v>
       </c>
       <c r="G26" s="8">
-        <v>-2.16</v>
+        <v>-7.49</v>
       </c>
       <c r="H26" s="9">
         <v>0</v>
@@ -2544,25 +2544,25 @@
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7">
-        <v>128.5</v>
+        <v>116</v>
       </c>
       <c r="C27" s="7">
-        <v>116</v>
+        <v>113.5</v>
       </c>
       <c r="D27" s="7">
-        <v>138.5</v>
+        <v>117.5</v>
       </c>
       <c r="E27" s="7">
-        <v>113</v>
+        <v>99.5</v>
       </c>
       <c r="F27" s="8">
-        <v>-12.5</v>
+        <v>-2.5</v>
       </c>
       <c r="G27" s="8">
-        <v>-9.73</v>
+        <v>-2.16</v>
       </c>
       <c r="H27" s="9">
         <v>0</v>
@@ -2597,25 +2597,25 @@
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7">
-        <v>140</v>
+        <v>128.5</v>
       </c>
       <c r="C28" s="7">
-        <v>128.5</v>
+        <v>116</v>
       </c>
       <c r="D28" s="7">
-        <v>160</v>
+        <v>138.5</v>
       </c>
       <c r="E28" s="7">
-        <v>105.5</v>
+        <v>113</v>
       </c>
       <c r="F28" s="8">
-        <v>-11.5</v>
+        <v>-12.5</v>
       </c>
       <c r="G28" s="8">
-        <v>-8.2100000000000009</v>
+        <v>-9.73</v>
       </c>
       <c r="H28" s="9">
         <v>0</v>
@@ -2650,25 +2650,25 @@
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7">
-        <v>78.3</v>
+        <v>140</v>
       </c>
       <c r="C29" s="7">
-        <v>140</v>
+        <v>128.5</v>
       </c>
       <c r="D29" s="7">
-        <v>145.5</v>
+        <v>160</v>
       </c>
       <c r="E29" s="7">
-        <v>75.8</v>
-      </c>
-      <c r="F29" s="10">
-        <v>61.7</v>
-      </c>
-      <c r="G29" s="10">
-        <v>78.8</v>
+        <v>105.5</v>
+      </c>
+      <c r="F29" s="8">
+        <v>-11.5</v>
+      </c>
+      <c r="G29" s="8">
+        <v>-8.2100000000000009</v>
       </c>
       <c r="H29" s="9">
         <v>0</v>
@@ -2703,25 +2703,25 @@
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7">
-        <v>64.900000000000006</v>
+        <v>78.3</v>
       </c>
       <c r="C30" s="7">
-        <v>78.3</v>
+        <v>140</v>
       </c>
       <c r="D30" s="7">
-        <v>88.5</v>
+        <v>145.5</v>
       </c>
       <c r="E30" s="7">
-        <v>60</v>
+        <v>75.8</v>
       </c>
       <c r="F30" s="10">
-        <v>13.4</v>
+        <v>61.7</v>
       </c>
       <c r="G30" s="10">
-        <v>20.65</v>
+        <v>78.8</v>
       </c>
       <c r="H30" s="9">
         <v>0</v>
@@ -2756,25 +2756,25 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7">
-        <v>69.010000000000005</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="C31" s="7">
-        <v>64.900000000000006</v>
+        <v>78.3</v>
       </c>
       <c r="D31" s="7">
-        <v>77.14</v>
+        <v>88.5</v>
       </c>
       <c r="E31" s="7">
-        <v>48.82</v>
-      </c>
-      <c r="F31" s="8">
-        <v>-4.1100000000000003</v>
-      </c>
-      <c r="G31" s="8">
-        <v>-5.96</v>
+        <v>60</v>
+      </c>
+      <c r="F31" s="10">
+        <v>13.4</v>
+      </c>
+      <c r="G31" s="10">
+        <v>20.65</v>
       </c>
       <c r="H31" s="9">
         <v>0</v>
@@ -2809,25 +2809,25 @@
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7">
-        <v>49.99</v>
+        <v>69.010000000000005</v>
       </c>
       <c r="C32" s="7">
-        <v>69.010000000000005</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="D32" s="7">
-        <v>90.49</v>
+        <v>77.14</v>
       </c>
       <c r="E32" s="7">
-        <v>50</v>
-      </c>
-      <c r="F32" s="10">
-        <v>19.02</v>
-      </c>
-      <c r="G32" s="10">
-        <v>38.049999999999997</v>
+        <v>48.82</v>
+      </c>
+      <c r="F32" s="8">
+        <v>-4.1100000000000003</v>
+      </c>
+      <c r="G32" s="8">
+        <v>-5.96</v>
       </c>
       <c r="H32" s="9">
         <v>0</v>
@@ -2862,25 +2862,25 @@
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7">
-        <v>30.51</v>
+        <v>49.99</v>
       </c>
       <c r="C33" s="7">
-        <v>49.99</v>
+        <v>69.010000000000005</v>
       </c>
       <c r="D33" s="7">
-        <v>49.99</v>
+        <v>90.49</v>
       </c>
       <c r="E33" s="7">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F33" s="10">
-        <v>19.48</v>
+        <v>19.02</v>
       </c>
       <c r="G33" s="10">
-        <v>63.85</v>
+        <v>38.049999999999997</v>
       </c>
       <c r="H33" s="9">
         <v>0</v>
@@ -2915,25 +2915,25 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7">
-        <v>27.8</v>
+        <v>30.51</v>
       </c>
       <c r="C34" s="7">
-        <v>30.51</v>
+        <v>49.99</v>
       </c>
       <c r="D34" s="7">
-        <v>31.88</v>
+        <v>49.99</v>
       </c>
       <c r="E34" s="7">
-        <v>27.5</v>
+        <v>31</v>
       </c>
       <c r="F34" s="10">
-        <v>2.71</v>
+        <v>19.48</v>
       </c>
       <c r="G34" s="10">
-        <v>9.75</v>
+        <v>63.85</v>
       </c>
       <c r="H34" s="9">
         <v>0</v>
@@ -2968,25 +2968,25 @@
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7">
-        <v>29</v>
+        <v>27.8</v>
       </c>
       <c r="C35" s="7">
-        <v>27.8</v>
+        <v>30.51</v>
       </c>
       <c r="D35" s="7">
-        <v>29.26</v>
+        <v>31.88</v>
       </c>
       <c r="E35" s="7">
-        <v>27</v>
-      </c>
-      <c r="F35" s="8">
-        <v>-1.2</v>
-      </c>
-      <c r="G35" s="8">
-        <v>-4.1399999999999997</v>
+        <v>27.5</v>
+      </c>
+      <c r="F35" s="10">
+        <v>2.71</v>
+      </c>
+      <c r="G35" s="10">
+        <v>9.75</v>
       </c>
       <c r="H35" s="9">
         <v>0</v>
@@ -3021,25 +3021,25 @@
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C36" s="7">
-        <v>29</v>
+        <v>27.8</v>
       </c>
       <c r="D36" s="7">
-        <v>30.06</v>
+        <v>29.26</v>
       </c>
       <c r="E36" s="7">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="F36" s="8">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="G36" s="8">
-        <v>-3.33</v>
+        <v>-4.1399999999999997</v>
       </c>
       <c r="H36" s="9">
         <v>0</v>
@@ -3074,25 +3074,25 @@
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C37" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D37" s="7">
-        <v>33</v>
+        <v>30.06</v>
       </c>
       <c r="E37" s="7">
-        <v>30</v>
+        <v>27.3</v>
       </c>
       <c r="F37" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G37" s="8">
-        <v>-6.25</v>
+        <v>-3.33</v>
       </c>
       <c r="H37" s="9">
         <v>0</v>
@@ -3127,25 +3127,25 @@
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7">
-        <v>35.21</v>
+        <v>32</v>
       </c>
       <c r="C38" s="7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D38" s="7">
-        <v>35.99</v>
+        <v>33</v>
       </c>
       <c r="E38" s="7">
-        <v>31.82</v>
+        <v>30</v>
       </c>
       <c r="F38" s="8">
-        <v>-3.21</v>
+        <v>-2</v>
       </c>
       <c r="G38" s="8">
-        <v>-9.1199999999999992</v>
+        <v>-6.25</v>
       </c>
       <c r="H38" s="9">
         <v>0</v>
@@ -3180,25 +3180,25 @@
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7">
-        <v>36.61</v>
+        <v>35.21</v>
       </c>
       <c r="C39" s="7">
-        <v>35.21</v>
+        <v>32</v>
       </c>
       <c r="D39" s="7">
-        <v>37.880000000000003</v>
+        <v>35.99</v>
       </c>
       <c r="E39" s="7">
-        <v>35.200000000000003</v>
+        <v>31.82</v>
       </c>
       <c r="F39" s="8">
-        <v>-1.4</v>
+        <v>-3.21</v>
       </c>
       <c r="G39" s="8">
-        <v>-3.82</v>
+        <v>-9.1199999999999992</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
@@ -3233,25 +3233,25 @@
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7">
-        <v>37.79</v>
+        <v>36.61</v>
       </c>
       <c r="C40" s="7">
-        <v>36.61</v>
+        <v>35.21</v>
       </c>
       <c r="D40" s="7">
-        <v>37.99</v>
+        <v>37.880000000000003</v>
       </c>
       <c r="E40" s="7">
-        <v>35.81</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="F40" s="8">
-        <v>-1.18</v>
+        <v>-1.4</v>
       </c>
       <c r="G40" s="8">
-        <v>-3.12</v>
+        <v>-3.82</v>
       </c>
       <c r="H40" s="9">
         <v>0</v>
@@ -3286,25 +3286,25 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7">
-        <v>37.71</v>
+        <v>37.79</v>
       </c>
       <c r="C41" s="7">
-        <v>37.79</v>
+        <v>36.61</v>
       </c>
       <c r="D41" s="7">
-        <v>39.770000000000003</v>
+        <v>37.99</v>
       </c>
       <c r="E41" s="7">
-        <v>36.51</v>
-      </c>
-      <c r="F41" s="10">
-        <v>0.08</v>
-      </c>
-      <c r="G41" s="10">
-        <v>0.21</v>
+        <v>35.81</v>
+      </c>
+      <c r="F41" s="8">
+        <v>-1.18</v>
+      </c>
+      <c r="G41" s="8">
+        <v>-3.12</v>
       </c>
       <c r="H41" s="9">
         <v>0</v>
@@ -3339,25 +3339,25 @@
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7">
-        <v>38</v>
+        <v>37.71</v>
       </c>
       <c r="C42" s="7">
-        <v>37.71</v>
+        <v>37.79</v>
       </c>
       <c r="D42" s="7">
-        <v>38.83</v>
+        <v>39.770000000000003</v>
       </c>
       <c r="E42" s="7">
-        <v>36.909999999999997</v>
-      </c>
-      <c r="F42" s="8">
-        <v>-0.28999999999999998</v>
-      </c>
-      <c r="G42" s="8">
-        <v>-0.76</v>
+        <v>36.51</v>
+      </c>
+      <c r="F42" s="10">
+        <v>0.08</v>
+      </c>
+      <c r="G42" s="10">
+        <v>0.21</v>
       </c>
       <c r="H42" s="9">
         <v>0</v>
@@ -3392,25 +3392,25 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C43" s="7">
-        <v>38</v>
+        <v>37.71</v>
       </c>
       <c r="D43" s="7">
-        <v>40.5</v>
+        <v>38.83</v>
       </c>
       <c r="E43" s="7">
-        <v>37.21</v>
+        <v>36.909999999999997</v>
       </c>
       <c r="F43" s="8">
-        <v>-2</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="G43" s="8">
-        <v>-5</v>
+        <v>-0.76</v>
       </c>
       <c r="H43" s="9">
         <v>0</v>
@@ -3445,25 +3445,25 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7">
-        <v>39.450000000000003</v>
+        <v>40</v>
       </c>
       <c r="C44" s="7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D44" s="7">
-        <v>41.19</v>
+        <v>40.5</v>
       </c>
       <c r="E44" s="7">
-        <v>38</v>
-      </c>
-      <c r="F44" s="10">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G44" s="10">
-        <v>1.39</v>
+        <v>37.21</v>
+      </c>
+      <c r="F44" s="8">
+        <v>-2</v>
+      </c>
+      <c r="G44" s="8">
+        <v>-5</v>
       </c>
       <c r="H44" s="9">
         <v>0</v>
@@ -3498,25 +3498,25 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7">
-        <v>37.200000000000003</v>
+        <v>39.450000000000003</v>
       </c>
       <c r="C45" s="7">
-        <v>39.450000000000003</v>
+        <v>40</v>
       </c>
       <c r="D45" s="7">
-        <v>40.799999999999997</v>
+        <v>41.19</v>
       </c>
       <c r="E45" s="7">
-        <v>36.799999999999997</v>
+        <v>38</v>
       </c>
       <c r="F45" s="10">
-        <v>2.25</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G45" s="10">
-        <v>6.05</v>
+        <v>1.39</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
@@ -3551,25 +3551,25 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7">
-        <v>38.49</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="C46" s="7">
-        <v>37.200000000000003</v>
+        <v>39.450000000000003</v>
       </c>
       <c r="D46" s="7">
-        <v>40.200000000000003</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="E46" s="7">
-        <v>36</v>
-      </c>
-      <c r="F46" s="8">
-        <v>-1.29</v>
-      </c>
-      <c r="G46" s="8">
-        <v>-3.35</v>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F46" s="10">
+        <v>2.25</v>
+      </c>
+      <c r="G46" s="10">
+        <v>6.05</v>
       </c>
       <c r="H46" s="9">
         <v>0</v>
@@ -3604,25 +3604,25 @@
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7">
-        <v>40.01</v>
+        <v>38.49</v>
       </c>
       <c r="C47" s="7">
-        <v>38.49</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="D47" s="7">
-        <v>41.96</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="E47" s="7">
-        <v>36.979999999999997</v>
+        <v>36</v>
       </c>
       <c r="F47" s="8">
-        <v>-1.52</v>
+        <v>-1.29</v>
       </c>
       <c r="G47" s="8">
-        <v>-3.8</v>
+        <v>-3.35</v>
       </c>
       <c r="H47" s="9">
         <v>0</v>
@@ -3657,25 +3657,25 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7">
-        <v>49.01</v>
+        <v>40.01</v>
       </c>
       <c r="C48" s="7">
-        <v>40.01</v>
+        <v>38.49</v>
       </c>
       <c r="D48" s="7">
-        <v>63.99</v>
+        <v>41.96</v>
       </c>
       <c r="E48" s="7">
-        <v>36</v>
+        <v>36.979999999999997</v>
       </c>
       <c r="F48" s="8">
-        <v>-10</v>
+        <v>-1.52</v>
       </c>
       <c r="G48" s="8">
-        <v>-20</v>
+        <v>-3.8</v>
       </c>
       <c r="H48" s="9">
         <v>0</v>
@@ -3710,25 +3710,25 @@
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>17</v>
+        <v>43374</v>
+      </c>
+      <c r="B49" s="7">
+        <v>49.01</v>
+      </c>
+      <c r="C49" s="7">
+        <v>40.01</v>
+      </c>
+      <c r="D49" s="7">
+        <v>63.99</v>
+      </c>
+      <c r="E49" s="7">
+        <v>36</v>
+      </c>
+      <c r="F49" s="8">
+        <v>-10</v>
+      </c>
+      <c r="G49" s="8">
+        <v>-20</v>
       </c>
       <c r="H49" s="9">
         <v>0</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>17</v>
@@ -3816,54 +3816,107 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
+        <v>43313</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="9">
+        <v>0</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" s="9">
+        <v>0</v>
+      </c>
+      <c r="L51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M51" s="9">
+        <v>0</v>
+      </c>
+      <c r="N51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
         <v>43282</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" s="9">
-        <v>0</v>
-      </c>
-      <c r="I51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K51" s="9">
-        <v>0</v>
-      </c>
-      <c r="L51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M51" s="9">
-        <v>0</v>
-      </c>
-      <c r="N51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P51" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="9" t="s">
+      <c r="B52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" s="9">
+        <v>0</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" s="9">
+        <v>0</v>
+      </c>
+      <c r="L52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M52" s="9">
+        <v>0</v>
+      </c>
+      <c r="N52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P52" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="9" t="s">
         <v>17</v>
       </c>
     </row>
